--- a/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
+++ b/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
+++ b/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
+++ b/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
+++ b/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
+++ b/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
+++ b/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
+++ b/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
+++ b/fusionSectionsCDA/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
